--- a/files/afm-reyting-itogi-2026-10.xlsx
+++ b/files/afm-reyting-itogi-2026-10.xlsx
@@ -632,7 +632,7 @@
         <v/>
       </c>
       <c r="F7" s="5" t="n">
-        <v>2612884</v>
+        <v>2627761</v>
       </c>
       <c r="G7" s="6">
         <f>F7/10000</f>
@@ -673,14 +673,14 @@
         <v/>
       </c>
       <c r="F8" s="5" t="n">
-        <v>3755860</v>
+        <v>3763128</v>
       </c>
       <c r="G8" s="6">
         <f>F8/10000</f>
         <v/>
       </c>
       <c r="H8" s="5" t="n">
-        <v>2110</v>
+        <v>2150</v>
       </c>
       <c r="I8" s="6">
         <f>H8/50</f>

--- a/files/afm-reyting-itogi-2026-10.xlsx
+++ b/files/afm-reyting-itogi-2026-10.xlsx
@@ -632,14 +632,14 @@
         <v/>
       </c>
       <c r="F7" s="5" t="n">
-        <v>2627761</v>
+        <v>2632351</v>
       </c>
       <c r="G7" s="6">
         <f>F7/10000</f>
         <v/>
       </c>
       <c r="H7" s="5" t="n">
-        <v>1845</v>
+        <v>1850</v>
       </c>
       <c r="I7" s="6">
         <f>H7/50</f>
@@ -673,14 +673,14 @@
         <v/>
       </c>
       <c r="F8" s="5" t="n">
-        <v>3763128</v>
+        <v>3767700</v>
       </c>
       <c r="G8" s="6">
         <f>F8/10000</f>
         <v/>
       </c>
       <c r="H8" s="5" t="n">
-        <v>2150</v>
+        <v>2197</v>
       </c>
       <c r="I8" s="6">
         <f>H8/50</f>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" s="5" t="n">
-        <v>2165911</v>
+        <v>2166231</v>
       </c>
       <c r="G10" s="6">
         <f>F10/10000</f>
@@ -796,7 +796,7 @@
         <v/>
       </c>
       <c r="F11" s="5" t="n">
-        <v>2259469</v>
+        <v>2259589</v>
       </c>
       <c r="G11" s="6">
         <f>F11/10000</f>
@@ -837,7 +837,7 @@
         <v/>
       </c>
       <c r="F12" s="5" t="n">
-        <v>3221763</v>
+        <v>3222003</v>
       </c>
       <c r="G12" s="6">
         <f>F12/10000</f>
@@ -919,7 +919,7 @@
         <v/>
       </c>
       <c r="F14" s="5" t="n">
-        <v>1221762</v>
+        <v>1222182</v>
       </c>
       <c r="G14" s="6">
         <f>F14/10000</f>
@@ -960,7 +960,7 @@
         <v/>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1719819</v>
+        <v>1719939</v>
       </c>
       <c r="G15" s="6">
         <f>F15/10000</f>
@@ -1001,7 +1001,7 @@
         <v/>
       </c>
       <c r="F16" s="5" t="n">
-        <v>1545180</v>
+        <v>1546180</v>
       </c>
       <c r="G16" s="6">
         <f>F16/10000</f>
@@ -1042,7 +1042,7 @@
         <v/>
       </c>
       <c r="F17" s="5" t="n">
-        <v>2328640</v>
+        <v>2328650</v>
       </c>
       <c r="G17" s="6">
         <f>F17/10000</f>
@@ -1083,7 +1083,7 @@
         <v/>
       </c>
       <c r="F18" s="5" t="n">
-        <v>1093250</v>
+        <v>1093800</v>
       </c>
       <c r="G18" s="6">
         <f>F18/10000</f>
@@ -1247,7 +1247,7 @@
         <v/>
       </c>
       <c r="F22" s="5" t="n">
-        <v>1249791</v>
+        <v>1250151</v>
       </c>
       <c r="G22" s="6">
         <f>F22/10000</f>
@@ -1370,7 +1370,7 @@
         <v/>
       </c>
       <c r="F25" s="5" t="n">
-        <v>198190</v>
+        <v>198400</v>
       </c>
       <c r="G25" s="6">
         <f>F25/10000</f>
